--- a/data/trans_bre/P1404-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1404-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,18</t>
+          <t>0,52; 6,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 5,58</t>
+          <t>-1,91; 5,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 6,5</t>
+          <t>-0,7; 6,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,91</t>
+          <t>-1,11; 5,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 114,02</t>
+          <t>6,15; 113,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 48,67</t>
+          <t>-13,54; 52,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 61,52</t>
+          <t>-5,34; 64,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 47,31</t>
+          <t>-6,57; 44,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,35</t>
+          <t>-0,18; 5,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,97</t>
+          <t>-0,19; 5,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,94</t>
+          <t>-0,28; 5,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 11,02</t>
+          <t>-0,8; 4,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 69,22</t>
+          <t>-2,37; 70,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 62,41</t>
+          <t>-1,9; 58,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 55,48</t>
+          <t>-2,89; 53,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 172,18</t>
+          <t>-5,2; 37,5</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,79</t>
+          <t>-2,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>109,04%</t>
+          <t>-13,05%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,54</t>
+          <t>0,13; 6,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 6,13</t>
+          <t>-0,85; 6,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 1,99</t>
+          <t>-4,66; 1,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 51,25</t>
+          <t>-5,13; 1,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 109,64</t>
+          <t>1,09; 109,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 71,87</t>
+          <t>-7,88; 73,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 20,38</t>
+          <t>-33,76; 17,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 363,58</t>
+          <t>-30,11; 9,26</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,58</t>
+          <t>-1,59; 3,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 5,15</t>
+          <t>-0,76; 5,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,77</t>
+          <t>-0,25; 5,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,53</t>
+          <t>1,44; 6,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 52,44</t>
+          <t>-17,28; 47,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 51,69</t>
+          <t>-5,44; 55,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 73,17</t>
+          <t>-2,56; 69,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 50,61</t>
+          <t>9,45; 57,17</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,75</t>
+          <t>1,03; 3,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,1</t>
+          <t>0,66; 3,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,34</t>
+          <t>0,18; 3,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 23,11</t>
+          <t>0,13; 3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,48; 51,37</t>
+          <t>12,4; 54,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 39,16</t>
+          <t>4,85; 37,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 31,67</t>
+          <t>1,51; 32,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,24; 180,81</t>
+          <t>0,83; 24,69</t>
         </is>
       </c>
     </row>
